--- a/自动计算新Origin.xlsx
+++ b/自动计算新Origin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Steam\steamapps\common\Barotrauma\LocalMods\Barotrauma-Animated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B00B68A-E593-48C5-A9DE-C005C6B73D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECC0A5B-8AF4-40ED-87B3-1EF9E505855A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18700" yWindow="3480" windowWidth="13980" windowHeight="14830" xr2:uid="{17553075-8736-4640-860F-CEC96F7F594E}"/>
+    <workbookView xWindow="18920" yWindow="3700" windowWidth="13980" windowHeight="14830" xr2:uid="{17553075-8736-4640-860F-CEC96F7F594E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -557,19 +557,19 @@
         <v>272</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1">
         <v>64</v>
       </c>
       <c r="D3" s="1">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="E3" s="1">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="F3" s="1">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -609,21 +609,21 @@
         <v>272</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="C6" s="1">
         <v>64</v>
       </c>
       <c r="D6" s="1">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E6" s="1">
         <f>(A3+C3*E3-A6)/C6</f>
-        <v>0.5</v>
+        <v>0.48000000000000043</v>
       </c>
       <c r="F6" s="1">
         <f>(B3+D3*F3-B6)/D6</f>
-        <v>0.54545454545454541</v>
+        <v>0.41250000000000009</v>
       </c>
     </row>
   </sheetData>
